--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,38 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>포인티PT 서울대입구 본점</t>
+          <t>제임스킬짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pointpt_@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>teddy@piehealthcare.kr</t>
-        </is>
-      </c>
+          <t>wan4545@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1485-0371</t>
+          <t>0507-1303-9645</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1808 4층 포인티PT 서울대입구 본점</t>
+          <t>서울특별시 관악구 관악로 163 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.pointpt.training/</t>
+          <t>https://smartstore.naver.com/jameskill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>179</v>
+        <v>899</v>
       </c>
       <c r="Q2" t="n">
-        <v>1309</v>
+        <v>1628</v>
       </c>
       <c r="R2" t="n">
-        <v>1488</v>
+        <v>2527</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1707961869</t>
+          <t>37207749</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707961869</t>
+          <t>https://m.place.naver.com/place/37207749</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
+          <t>프로틴짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>youni_gym@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-9990</t>
+          <t>0507-1415-9682</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로64길 9 3층</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youni_gym</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -710,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>643</v>
+        <v>315</v>
       </c>
       <c r="Q3" t="n">
-        <v>1996</v>
+        <v>515</v>
       </c>
       <c r="R3" t="n">
-        <v>2639</v>
+        <v>830</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1359477400</t>
+          <t>1401058700</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359477400</t>
+          <t>https://m.place.naver.com/place/1401058700</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용PT 폴인핏 신림역점</t>
+          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sillimpt@naver.com</t>
+          <t>mggym6772@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1434-1561</t>
+          <t>0507-1368-6772</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로67길 9 3층</t>
+          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fall_in_fit_</t>
+          <t>http://pf.kakao.com/_qNFjn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -804,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>1085</v>
+        <v>825</v>
       </c>
       <c r="R4" t="n">
-        <v>1399</v>
+        <v>1060</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1762308656</t>
+          <t>1914913731</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1762308656</t>
+          <t>https://m.place.naver.com/place/1914913731</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>제임스킬짐PT 서울대입구점</t>
+          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wan4545@naver.com</t>
+          <t>youni_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1303-9645</t>
+          <t>0507-1375-9990</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 163 3층</t>
+          <t>서울특별시 관악구 신림로64길 9 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jameskill</t>
+          <t>https://blog.naver.com/youni_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>892</v>
+        <v>643</v>
       </c>
       <c r="Q5" t="n">
-        <v>1625</v>
+        <v>2063</v>
       </c>
       <c r="R5" t="n">
-        <v>2517</v>
+        <v>2706</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37207749</t>
+          <t>1359477400</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37207749</t>
+          <t>https://m.place.naver.com/place/1359477400</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>핏라운지PT 신림점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mggym6772@naver.com</t>
+          <t>fitlounge01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1368-6772</t>
+          <t>0507-1310-9499</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>https://blog.naver.com/fitlounge01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -992,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="Q6" t="n">
-        <v>1014</v>
+        <v>658</v>
       </c>
       <c r="R6" t="n">
-        <v>1245</v>
+        <v>771</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1914913731</t>
+          <t>1429308054</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914913731</t>
+          <t>https://m.place.naver.com/place/1429308054</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="Q2" t="n">
         <v>1628</v>
       </c>
       <c r="R2" t="n">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로틴짐PT 서울대입구점</t>
+          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>proteingym_seoul@naver.com</t>
+          <t>mggym6772@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-9682</t>
+          <t>0507-1368-6772</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
+          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>http://pf.kakao.com/_qNFjn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="Q3" t="n">
-        <v>515</v>
+        <v>825</v>
       </c>
       <c r="R3" t="n">
-        <v>830</v>
+        <v>1061</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1401058700</t>
+          <t>1914913731</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401058700</t>
+          <t>https://m.place.naver.com/place/1914913731</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>프로틴짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mggym6772@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-6772</t>
+          <t>0507-1415-9682</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="Q4" t="n">
-        <v>825</v>
+        <v>516</v>
       </c>
       <c r="R4" t="n">
-        <v>1060</v>
+        <v>831</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1914913731</t>
+          <t>1401058700</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914913731</t>
+          <t>https://m.place.naver.com/place/1401058700</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
+          <t>핏라운지PT 신림점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>youni_gym@naver.com</t>
+          <t>fitlounge01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-9990</t>
+          <t>0507-1310-9499</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로64길 9 3층</t>
+          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youni_gym</t>
+          <t>https://blog.naver.com/fitlounge01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>643</v>
+        <v>113</v>
       </c>
       <c r="Q5" t="n">
-        <v>2063</v>
+        <v>658</v>
       </c>
       <c r="R5" t="n">
-        <v>2706</v>
+        <v>771</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1359477400</t>
+          <t>1429308054</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359477400</t>
+          <t>https://m.place.naver.com/place/1429308054</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핏라운지PT 신림점</t>
+          <t>리메이크바디샵 낙성대 본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitlounge01@naver.com</t>
+          <t>chance7665@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1310-9499</t>
+          <t>0507-1387-7665</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
+          <t>서울특별시 관악구 남부순환로 1888 지하1층 2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>https://youtube.com/@rblab</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>113</v>
+        <v>566</v>
       </c>
       <c r="Q6" t="n">
-        <v>658</v>
+        <v>732</v>
       </c>
       <c r="R6" t="n">
-        <v>771</v>
+        <v>1298</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1429308054</t>
+          <t>116799071</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429308054</t>
+          <t>https://m.place.naver.com/place/116799071</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제임스킬짐PT 서울대입구점</t>
+          <t>피지오숲 필라테스&amp;PT 신림보라매점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wan4545@naver.com</t>
+          <t>physioforest@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1303-9645</t>
+          <t>0507-1345-1130</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 163 3층</t>
+          <t>서울 관악구 봉천로 223 4층, 5층 피지오숲</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jameskill</t>
+          <t>https://blog.naver.com/physioforest</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,18 +601,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461pz</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>900</v>
+        <v>788</v>
       </c>
       <c r="Q2" t="n">
-        <v>1628</v>
+        <v>555</v>
       </c>
       <c r="R2" t="n">
-        <v>2528</v>
+        <v>1343</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37207749</t>
+          <t>1464882121</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37207749</t>
+          <t>https://m.place.naver.com/place/1464882121</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>제임스킬짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mggym6772@naver.com</t>
+          <t>wan4545@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1368-6772</t>
+          <t>0507-1303-9645</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울 관악구 관악로 163 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>https://smartstore.naver.com/jameskill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,13 +704,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2s42</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>236</v>
+        <v>900</v>
       </c>
       <c r="Q3" t="n">
-        <v>825</v>
+        <v>1628</v>
       </c>
       <c r="R3" t="n">
-        <v>1061</v>
+        <v>2528</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1914913731</t>
+          <t>37207749</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914913731</t>
+          <t>https://m.place.naver.com/place/37207749</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로틴짐PT 서울대입구점</t>
+          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>proteingym_seoul@naver.com</t>
+          <t>mggym6772@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-9682</t>
+          <t>0507-1368-6772</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
+          <t>서울 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>http://pf.kakao.com/_qNFjn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,18 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wspv2e8</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="Q4" t="n">
-        <v>516</v>
+        <v>825</v>
       </c>
       <c r="R4" t="n">
-        <v>831</v>
+        <v>1061</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1401058700</t>
+          <t>1914913731</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401058700</t>
+          <t>https://m.place.naver.com/place/1914913731</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핏라운지PT 신림점</t>
+          <t>프로틴짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitlounge01@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1310-9499</t>
+          <t>0507-1415-9682</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
+          <t>서울 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5upc0</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>113</v>
+        <v>315</v>
       </c>
       <c r="Q5" t="n">
-        <v>658</v>
+        <v>516</v>
       </c>
       <c r="R5" t="n">
-        <v>771</v>
+        <v>831</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1429308054</t>
+          <t>1401058700</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429308054</t>
+          <t>https://m.place.naver.com/place/1401058700</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리메이크바디샵 낙성대 본점</t>
+          <t>핏라운지PT 신림점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>chance7665@naver.com</t>
+          <t>fitlounge01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1387-7665</t>
+          <t>0507-1310-9499</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1888 지하1층 2호</t>
+          <t>서울 관악구 남부순환로 1630 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@rblab</t>
+          <t>https://blog.naver.com/fitlounge01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wickvkq</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>566</v>
+        <v>113</v>
       </c>
       <c r="Q6" t="n">
-        <v>732</v>
+        <v>658</v>
       </c>
       <c r="R6" t="n">
-        <v>1298</v>
+        <v>771</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>116799071</t>
+          <t>1429308054</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/116799071</t>
+          <t>https://m.place.naver.com/place/1429308054</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1027,20 +1047,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>리메이크바디샵 낙성대 본점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>chance7665@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1387-7665</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>서울 관악구 남부순환로 1888 지하1층 2호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@rblab</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1050,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1060,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4drwa</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1071,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2600002</t>
+          <t>116799071</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600002</t>
+          <t>https://m.place.naver.com/place/116799071</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1168,15 +1208,93 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>2600002</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2600002</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>7251063</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7251063</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 관악구 관악로 163 3층</t>
+          <t>서울특별시 관악구 관악로 163 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2s42</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wspv2e8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -875,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 관악구 관악로 186 지하1층 B02호</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5upc0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 관악구 남부순환로 1630 지하1층</t>
+          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wickvkq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1004,10 @@
         <v>113</v>
       </c>
       <c r="Q6" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="R6" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리메이크바디샵 낙성대 본점</t>
+          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chance7665@naver.com</t>
+          <t>youni_gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1387-7665</t>
+          <t>0507-1375-9990</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 관악구 남부순환로 1888 지하1층 2호</t>
+          <t>서울특별시 관악구 신림로64길 9 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@rblab</t>
+          <t>https://blog.naver.com/youni_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,22 +1075,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4drwa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>566</v>
+        <v>643</v>
       </c>
       <c r="Q7" t="n">
-        <v>732</v>
+        <v>2075</v>
       </c>
       <c r="R7" t="n">
-        <v>1298</v>
+        <v>2718</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>116799071</t>
+          <t>1359477400</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/116799071</t>
+          <t>https://m.place.naver.com/place/1359477400</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physioforest</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jameskill</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2s42</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -778,17 +782,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wspv2e8</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -872,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5upc0</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -966,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wickvkq</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1060,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youni_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hrwy</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="Q7" t="n">
         <v>2075</v>
       </c>
       <c r="R7" t="n">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피지오숲 필라테스&amp;PT 신림보라매점</t>
+          <t>제임스킬짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>physioforest@naver.com</t>
+          <t>wan4545@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1345-1130</t>
+          <t>0507-1303-9645</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 관악구 봉천로 223 4층, 5층 피지오숲</t>
+          <t>서울특별시 관악구 관악로 163 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/jameskill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w461pz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>788</v>
+        <v>900</v>
       </c>
       <c r="Q2" t="n">
-        <v>555</v>
+        <v>1628</v>
       </c>
       <c r="R2" t="n">
-        <v>1343</v>
+        <v>2528</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1464882121</t>
+          <t>37207749</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1464882121</t>
+          <t>https://m.place.naver.com/place/37207749</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,39 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제임스킬짐PT 서울대입구점</t>
+          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wan4545@naver.com</t>
+          <t>mggym6772@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1303-9645</t>
+          <t>0507-1368-6772</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 163 3층</t>
+          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_qNFjn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,17 +700,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2s42</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>900</v>
+        <v>236</v>
       </c>
       <c r="Q3" t="n">
-        <v>1628</v>
+        <v>825</v>
       </c>
       <c r="R3" t="n">
-        <v>2528</v>
+        <v>1061</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37207749</t>
+          <t>1914913731</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37207749</t>
+          <t>https://m.place.naver.com/place/1914913731</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>프로틴짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mggym6772@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-6772</t>
+          <t>0507-1415-9682</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,27 +784,23 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wspv2e8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="Q4" t="n">
-        <v>825</v>
+        <v>516</v>
       </c>
       <c r="R4" t="n">
-        <v>1061</v>
+        <v>831</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1914913731</t>
+          <t>1401058700</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914913731</t>
+          <t>https://m.place.naver.com/place/1401058700</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로틴짐PT 서울대입구점</t>
+          <t>핏라운지PT 신림점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>proteingym_seoul@naver.com</t>
+          <t>fitlounge01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1415-9682</t>
+          <t>0507-1310-9499</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
+          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitlounge01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5upc0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>315</v>
+        <v>113</v>
       </c>
       <c r="Q5" t="n">
-        <v>516</v>
+        <v>659</v>
       </c>
       <c r="R5" t="n">
-        <v>831</v>
+        <v>772</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1401058700</t>
+          <t>1429308054</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401058700</t>
+          <t>https://m.place.naver.com/place/1429308054</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핏라운지PT 신림점</t>
+          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitlounge01@naver.com</t>
+          <t>youni_gym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1310-9499</t>
+          <t>0507-1375-9990</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 남부순환로 1630 지하1층</t>
+          <t>서울특별시 관악구 신림로64길 9 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/youni_gym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,27 +972,23 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wickvkq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>113</v>
+        <v>642</v>
       </c>
       <c r="Q6" t="n">
-        <v>659</v>
+        <v>2075</v>
       </c>
       <c r="R6" t="n">
-        <v>772</v>
+        <v>2717</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,46 +1012,30 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1429308054</t>
+          <t>1359477400</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429308054</t>
+          <t>https://m.place.naver.com/place/1359477400</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>youni_gym@naver.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1375-9990</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로64길 9 3층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,32 +1060,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4hrwy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2075</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2717</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1359477400</t>
+          <t>2600002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359477400</t>
+          <t>https://m.place.naver.com/place/2600002</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1208,95 +1168,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2600002</t>
+          <t>7251063</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600002</t>
+          <t>https://m.place.naver.com/place/7251063</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>7251063</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7251063</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -1000,10 +1000,10 @@
         <v>642</v>
       </c>
       <c r="Q6" t="n">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="R6" t="n">
-        <v>2717</v>
+        <v>2720</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jameskill</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2s42</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -774,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5upc0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -868,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wickvkq</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유앤아이짐 헬스&amp;PT 신림역점</t>
+          <t>리메이크바디샵 낙성대 본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>youni_gym@naver.com</t>
+          <t>chance7665@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1375-9990</t>
+          <t>0507-1387-7665</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 신림로64길 9 3층</t>
+          <t>서울특별시 관악구 남부순환로 1888 지하1층 2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youni_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,38 +984,42 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4drwa</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P6" t="n">
-        <v>642</v>
+        <v>567</v>
       </c>
       <c r="Q6" t="n">
-        <v>2078</v>
+        <v>733</v>
       </c>
       <c r="R6" t="n">
-        <v>2720</v>
+        <v>1300</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1359477400</t>
+          <t>116799071</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359477400</t>
+          <t>https://m.place.naver.com/place/116799071</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/jameskill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2s42</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -722,10 +718,10 @@
         <v>236</v>
       </c>
       <c r="Q3" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="R3" t="n">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -778,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5upc0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -820,10 +812,10 @@
         <v>315</v>
       </c>
       <c r="Q4" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="R4" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -876,7 +868,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitlounge01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wickvkq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -974,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@rblab</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4drwa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1038,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -624,10 +624,10 @@
         <v>900</v>
       </c>
       <c r="Q2" t="n">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="R2" t="n">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>프로틴짐PT 서울대입구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mggym6772@naver.com</t>
+          <t>proteingym_seoul@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1368-6772</t>
+          <t>0507-1415-9682</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
+          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>https://blog.naver.com/proteingym_seoul</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="Q3" t="n">
-        <v>826</v>
+        <v>519</v>
       </c>
       <c r="R3" t="n">
-        <v>1062</v>
+        <v>834</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1914913731</t>
+          <t>1401058700</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914913731</t>
+          <t>https://m.place.naver.com/place/1401058700</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로틴짐PT 서울대입구점</t>
+          <t>미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>proteingym_seoul@naver.com</t>
+          <t>mggym6772@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-9682</t>
+          <t>0507-1368-6772</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 관악구 관악로 186 지하1층 B02호</t>
+          <t>서울특별시 관악구 은천로 37 정암빌딩 7층 미래가그려짐 PT&amp;헬스 봉천역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>http://pf.kakao.com/_qNFjn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="Q4" t="n">
-        <v>517</v>
+        <v>825</v>
       </c>
       <c r="R4" t="n">
-        <v>832</v>
+        <v>1061</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1401058700</t>
+          <t>1914913731</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401058700</t>
+          <t>https://m.place.naver.com/place/1914913731</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="Q6" t="n">
         <v>733</v>
       </c>
       <c r="R6" t="n">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="Q2" t="n">
         <v>1623</v>
       </c>
       <c r="R2" t="n">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q4" t="n">
         <v>825</v>
       </c>
       <c r="R4" t="n">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/관악_PT.xlsx
+++ b/naver-place-crawler/results_health/관악_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/jameskill</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2s42</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/proteingym_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,38 +694,42 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5upc0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
         <v>519</v>
       </c>
       <c r="R3" t="n">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -774,30 +782,34 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qNFjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wspv2e8</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -868,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitlounge01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wickvkq</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -962,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@rblab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4drwa</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
